--- a/stories/arbres/TREE-DIF-010.xlsx
+++ b/stories/arbres/TREE-DIF-010.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lina est au bord de la mer, avec maman. Papa porte le sac. Un camarade court sur le sable. Il a beaucoup d'énergie. Maman dit : cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Lina est au bord de la mer, avec maman. Papa porte le sac. Un camarade court sur le sable. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lina est au bord de la mer, avec maman. Papa porte le sac. Un camarade court sur le sable. Il a beaucoup d'énergie.
+maman|Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1677,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers le bac à sable. Un camarade court, saute, creuse. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Lina peut jouer ou attendre. Maman est là. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Beaucoup d'énergie, c'est une faute ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Lina respire. Maman est là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, Lina sort les cubes. Le camarade bouge beaucoup. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le bac à sable. Puis les cubes. Puis rouge. Un ballon s'immobilise. Lina pose les cubes à sa place. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lina s'arrête près de bleu. les cubes est rangé. On se tient la main. Lina écoute maman encore une fois. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lina se souvient de le bac à sable. Et de les cubes. Et de vert. On range un objet. Lina enfile ses chaussons. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3531,7 +3619,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Au bac, Lina ouvre le livre. Le camarade tourne, puis s'assoit. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman dit : je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Au bac, Lina ouvre le livre. Le camarade tourne, puis s'assoit. Cette énergie n'est pas une faute. On peut jouer ou attendre. Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3669,6 +3757,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, Lina ouvre le livre. Le camarade tourne, puis s'assoit. Cette énergie n'est pas une faute. On peut jouer ou attendre.
+maman|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3951,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4120,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le livre. Près de le bac à sable. Lina s'arrête. Une feuille tombe. Lina boit une gorgée d'eau. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4287,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4207,7 +4316,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Lina range le livre. bleu reste près de le bac à sable. Le vent est doux. Lina dit : j'ai appris. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Lina range le livre. bleu reste près de le bac à sable. Le vent est doux. J'ai appris. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4345,6 +4454,13 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lina range le livre. bleu reste près de le bac à sable. Le vent est doux.
+enfant-f|J'ai appris. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte.
+narrateur|Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4623,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4531,7 +4652,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le livre aussi. le bac à sable reste dans le souvenir. On attend son tour. Lina tend vert à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Vert est là. le livre aussi. le bac à sable reste dans le souvenir. On attend son tour. Lina tend vert à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4669,6 +4790,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le livre aussi. le bac à sable reste dans le souvenir. On attend son tour. Lina tend vert à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4957,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5124,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, Lina sort la dînette. Le camarade sert très vite. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5317,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5486,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint rouge. la dînette est rangé. le bac à sable est fini. Le savon sent bon. Lina sourit. Maman sourit aussi. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5653,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5820,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Lina pose la dînette. le bac à sable est derrière. On dit merci. Lina range la tasse. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5987,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6154,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lina montre vert. Maman a vu le bac à sable. Et la dînette. Un crochet tient bien le manteau. Lina répète tout bas le geste. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6321,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6317,6 +6488,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers le toboggan. Un camarade monte, descend, recommence. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Lina peut jouer ou attendre. Papa porte le sac. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6493,6 +6669,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On joue, ou on attend ?</t>
         </is>
       </c>
     </row>
@@ -6661,6 +6842,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Lina retient le geste. Maman sourit. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6847,6 +7033,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6871,7 +7062,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Au toboggan, Lina a les cubes. Le camarade monte encore. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman dit : je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Au toboggan, Lina a les cubes. Le camarade monte encore. Cette énergie n'est pas une faute. On peut jouer ou attendre. Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7009,6 +7200,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Au toboggan, Lina a les cubes. Le camarade monte encore. Cette énergie n'est pas une faute. On peut jouer ou attendre.
+maman|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7197,6 +7394,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -7361,6 +7563,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le toboggan. Puis les cubes. Puis rouge. Ça sent le pain chaud. Lina montre rouge à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7523,6 +7730,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7685,6 +7897,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lina s'arrête près de bleu. les cubes est rangé. Un ruban reste dans la poche. Lina pose sa tête un moment. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7847,6 +8064,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8009,6 +8231,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lina se souvient de le toboggan. Et de les cubes. Et de vert. Le sol est un peu froid. Lina marche près de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8171,6 +8398,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8333,6 +8565,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Au toboggan, Lina a le livre. Le camarade attend une seconde. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8521,6 +8758,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8685,6 +8927,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le livre. Près de le toboggan. Lina s'arrête. On écoute jusqu'au bout. Lina souffle, puis sourit à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8847,6 +9094,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9009,6 +9261,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lina range le livre. bleu reste près de le toboggan. Une cloche tinte, tout loin. Lina s'assoit près de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9171,6 +9428,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9195,7 +9457,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le livre aussi. le toboggan reste dans le souvenir. Il y a des miettes sur la table. Lina ferme le sac. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Vert est là. le livre aussi. le toboggan reste dans le souvenir. Il y a des miettes sur la table. Lina ferme le sac. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9333,6 +9595,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le livre aussi. le toboggan reste dans le souvenir. Il y a des miettes sur la table. Lina ferme le sac. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9495,6 +9762,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9657,6 +9929,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Au toboggan, Lina a la dînette. Le camarade rit. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9845,6 +10122,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -10009,6 +10291,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint rouge. la dînette est rangé. le toboggan est fini. L'eau coule, tout petit bruit. Lina ferme la porte, tout doux. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10171,6 +10458,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10333,6 +10625,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Lina pose la dînette. le toboggan est derrière. La couverture est douce. Lina prend la main de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10495,6 +10792,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10657,6 +10959,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lina montre vert. Maman a vu le toboggan. Et la dînette. Une tasse cliquette. Lina serre la main de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10819,6 +11126,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10981,6 +11293,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers les balançoires. Un camarade pousse fort, puis rit. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Lina peut jouer ou attendre. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11157,6 +11474,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On demande à un adulte ?</t>
         </is>
       </c>
     </row>
@@ -11325,6 +11647,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Lina hoche la tête. On continue, avec maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11511,6 +11838,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11673,6 +12005,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Aux balançoires, Lina a les cubes. Le camarade pousse. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11861,6 +12198,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12025,6 +12367,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi les balançoires. Puis les cubes. Puis rouge. Un linge sèche à l'air. Lina dit merci à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12187,6 +12534,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12349,6 +12701,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lina s'arrête près de bleu. les cubes est rangé. Un chat miaule une fois. Lina plie un pull. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12511,6 +12868,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12673,6 +13035,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lina se souvient de les balançoires. Et de les cubes. Et de vert. Une chaussette est encore sablée. Papa n'est pas loin. Lina les rejoint. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12835,6 +13202,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12997,6 +13369,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Aux balançoires, Lina a le livre. Le camarade s'assoit. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13185,6 +13562,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -13349,6 +13731,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le livre. Près de les balançoires. Lina s'arrête. Un vélo passe au loin. Lina caresse le doudou. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13511,6 +13898,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13673,6 +14065,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lina range le livre. bleu reste près de les balançoires. Les chaussures font toc toc. Lina range les balançoires dans sa tête, comme un souvenir. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13835,6 +14232,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13859,7 +14261,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le livre aussi. les balançoires reste dans le souvenir. On entend un oiseau. Lina raccroche un linge. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Vert est là. le livre aussi. les balançoires reste dans le souvenir. On entend un oiseau. Lina raccroche un linge. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13997,6 +14399,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le livre aussi. les balançoires reste dans le souvenir. On entend un oiseau. Lina raccroche un linge. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14159,6 +14566,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14183,7 +14595,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Aux balançoires, Lina a la dînette. Le camarade souffle. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman dit : je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Aux balançoires, Lina a la dînette. Le camarade souffle. Cette énergie n'est pas une faute. On peut jouer ou attendre. Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14321,6 +14733,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Aux balançoires, Lina a la dînette. Le camarade souffle. Cette énergie n'est pas une faute. On peut jouer ou attendre.
+maman|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14509,6 +14927,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14673,6 +15096,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint rouge. la dînette est rangé. les balançoires est fini. On souffle doucement. Lina chuchote : c'est fini. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14835,6 +15263,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14997,6 +15430,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Lina pose la dînette. les balançoires est derrière. Une pomme brille un peu. Lina range encore un peu, près de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15159,6 +15597,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15321,6 +15764,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lina montre vert. Maman a vu les balançoires. Et la dînette. On rit un peu. Lina essuie ses mains. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15483,6 +15931,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15501,7 +15954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15574,6 +16027,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-010.xlsx
+++ b/stories/arbres/TREE-DIF-010.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 maman|Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
           <t>narrateur|Lina va vers le bac à sable. Un camarade court, saute, creuse. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Lina peut jouer ou attendre. Maman est là. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Beaucoup d'énergie, c'est une faute ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Lina respire. Maman est là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Au bac, Lina sort les cubes. Le camarade bouge beaucoup. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Lina a choisi le bac à sable. Puis les cubes. Puis rouge. Un ballon s'immobilise. Lina pose les cubes à sa place. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Lina s'arrête près de bleu. les cubes est rangé. On se tient la main. Lina écoute maman encore une fois. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Lina se souvient de le bac à sable. Et de les cubes. Et de vert. On range un objet. Lina enfile ses chaussons. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3763,6 +3782,7 @@
 maman|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3958,6 +3978,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4125,6 +4146,7 @@
           <t>narrateur|Avec rouge. Après le livre. Près de le bac à sable. Lina s'arrête. Une feuille tombe. Lina boit une gorgée d'eau. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4292,6 +4314,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4461,6 +4484,7 @@
 narrateur|Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4628,6 +4652,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4795,6 +4820,7 @@
           <t>narrateur|Vert est là. le livre aussi. le bac à sable reste dans le souvenir. On attend son tour. Lina tend vert à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4962,6 +4988,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5129,6 +5156,7 @@
           <t>narrateur|Au bac, Lina sort la dînette. Le camarade sert très vite. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5324,6 +5352,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5491,6 +5520,7 @@
           <t>narrateur|Lina rejoint rouge. la dînette est rangé. le bac à sable est fini. Le savon sent bon. Lina sourit. Maman sourit aussi. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5658,6 +5688,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5825,6 +5856,7 @@
           <t>narrateur|Près de bleu. Lina pose la dînette. le bac à sable est derrière. On dit merci. Lina range la tasse. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5992,6 +6024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6159,6 +6192,7 @@
           <t>narrateur|Lina montre vert. Maman a vu le bac à sable. Et la dînette. Un crochet tient bien le manteau. Lina répète tout bas le geste. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6326,6 +6360,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6493,6 +6528,7 @@
           <t>narrateur|Lina va vers le toboggan. Un camarade monte, descend, recommence. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Lina peut jouer ou attendre. Papa porte le sac. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6676,6 +6712,7 @@
           <t>narrateur|On joue, ou on attend ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6847,6 +6884,7 @@
           <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Lina retient le geste. Maman sourit. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7038,6 +7076,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7206,6 +7245,7 @@
 maman|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7401,6 +7441,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7568,6 +7609,7 @@
           <t>narrateur|Lina a choisi le toboggan. Puis les cubes. Puis rouge. Ça sent le pain chaud. Lina montre rouge à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7735,6 +7777,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7902,6 +7945,7 @@
           <t>narrateur|Lina s'arrête près de bleu. les cubes est rangé. Un ruban reste dans la poche. Lina pose sa tête un moment. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8069,6 +8113,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8236,6 +8281,7 @@
           <t>narrateur|Lina se souvient de le toboggan. Et de les cubes. Et de vert. Le sol est un peu froid. Lina marche près de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8403,6 +8449,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8570,6 +8617,7 @@
           <t>narrateur|Au toboggan, Lina a le livre. Le camarade attend une seconde. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8765,6 +8813,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8932,6 +8981,7 @@
           <t>narrateur|Avec rouge. Après le livre. Près de le toboggan. Lina s'arrête. On écoute jusqu'au bout. Lina souffle, puis sourit à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9099,6 +9149,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9266,6 +9317,7 @@
           <t>narrateur|Lina range le livre. bleu reste près de le toboggan. Une cloche tinte, tout loin. Lina s'assoit près de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9433,6 +9485,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9600,6 +9653,7 @@
           <t>narrateur|Vert est là. le livre aussi. le toboggan reste dans le souvenir. Il y a des miettes sur la table. Lina ferme le sac. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9767,6 +9821,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9934,6 +9989,7 @@
           <t>narrateur|Au toboggan, Lina a la dînette. Le camarade rit. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10129,6 +10185,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10296,6 +10353,7 @@
           <t>narrateur|Lina rejoint rouge. la dînette est rangé. le toboggan est fini. L'eau coule, tout petit bruit. Lina ferme la porte, tout doux. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10463,6 +10521,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10630,6 +10689,7 @@
           <t>narrateur|Près de bleu. Lina pose la dînette. le toboggan est derrière. La couverture est douce. Lina prend la main de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10797,6 +10857,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10964,6 +11025,7 @@
           <t>narrateur|Lina montre vert. Maman a vu le toboggan. Et la dînette. Une tasse cliquette. Lina serre la main de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11131,6 +11193,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11298,6 +11361,7 @@
           <t>narrateur|Lina va vers les balançoires. Un camarade pousse fort, puis rit. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Lina peut jouer ou attendre. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11481,6 +11545,7 @@
           <t>narrateur|On demande à un adulte ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11652,6 +11717,7 @@
           <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Lina hoche la tête. On continue, avec maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11843,6 +11909,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12010,6 +12077,7 @@
           <t>narrateur|Aux balançoires, Lina a les cubes. Le camarade pousse. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12205,6 +12273,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12372,6 +12441,7 @@
           <t>narrateur|Lina a choisi les balançoires. Puis les cubes. Puis rouge. Un linge sèche à l'air. Lina dit merci à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12539,6 +12609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12706,6 +12777,7 @@
           <t>narrateur|Lina s'arrête près de bleu. les cubes est rangé. Un chat miaule une fois. Lina plie un pull. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12873,6 +12945,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13040,6 +13113,7 @@
           <t>narrateur|Lina se souvient de les balançoires. Et de les cubes. Et de vert. Une chaussette est encore sablée. Papa n'est pas loin. Lina les rejoint. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13207,6 +13281,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13374,6 +13449,7 @@
           <t>narrateur|Aux balançoires, Lina a le livre. Le camarade s'assoit. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13569,6 +13645,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13736,6 +13813,7 @@
           <t>narrateur|Avec rouge. Après le livre. Près de les balançoires. Lina s'arrête. Un vélo passe au loin. Lina caresse le doudou. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13903,6 +13981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14070,6 +14149,7 @@
           <t>narrateur|Lina range le livre. bleu reste près de les balançoires. Les chaussures font toc toc. Lina range les balançoires dans sa tête, comme un souvenir. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14237,6 +14317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14404,6 +14485,7 @@
           <t>narrateur|Vert est là. le livre aussi. les balançoires reste dans le souvenir. On entend un oiseau. Lina raccroche un linge. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14571,6 +14653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14739,6 +14822,7 @@
 maman|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14934,6 +15018,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15101,6 +15186,7 @@
           <t>narrateur|Lina rejoint rouge. la dînette est rangé. les balançoires est fini. On souffle doucement. Lina chuchote : c'est fini. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15268,6 +15354,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15435,6 +15522,7 @@
           <t>narrateur|Près de bleu. Lina pose la dînette. les balançoires est derrière. Une pomme brille un peu. Lina range encore un peu, près de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15602,6 +15690,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15769,6 +15858,7 @@
           <t>narrateur|Lina montre vert. Maman a vu les balançoires. Et la dînette. On rit un peu. Lina essuie ses mains. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15936,6 +16026,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15954,7 +16045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16034,6 +16125,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16235,6 +16340,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-010.xlsx
+++ b/stories/arbres/TREE-DIF-010.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Un camarade qui bouge beaucoup — au bord de la mer</t>
+          <t>Le chapeau de paille et Raphaël qui saute</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le chapeau de paille sèche sur la rampe. Sarah voit Raphaël sauter près de la mer. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à papa ou maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lina est au bord de la mer, avec maman. Papa porte le sac. Un camarade court sur le sable. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Le chapeau de paille sèche sur la rampe. Une goutte de sel glisse, toute lente. Elle fait ploc sur le bois. Loin, une mouette crie, tout bas. La maison sent le linge chaud. Papa déplie une serviette rayée. Du sable colle déjà dans les chaussures. Maman verse de l'eau, dans une bouteille bleue. Tu sens le sel, Sarah ? Oui. Ça pique un peu. Les chaussures sont encore mouillées. Raphaël saute sur le chemin de sable. Ses pieds font toc, toc, toc. En ce moment, Sarah regarde le jeu, près de la mer. Un bac à sable. Un toboggan. Des balançoires. Il court, papa. Raphaël a beaucoup d'énergie. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. On va où ? Tu choisis, Sarah. La serviette rayée claque un peu, au vent. Le chapeau de paille sèche encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,11 +1337,40 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Lina est au bord de la mer, avec maman. Papa porte le sac. Un camarade court sur le sable. Il a beaucoup d'énergie.
-maman|Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le chapeau de paille sèche sur la rampe.
+narrateur|Une goutte de sel glisse, toute lente.
+narrateur|Elle fait ploc sur le bois.
+narrateur|Loin, une mouette crie, tout bas.
+narrateur|La maison sent le linge chaud.
+narrateur|Papa déplie une serviette rayée.
+narrateur|Du sable colle déjà dans les chaussures.
+narrateur|Maman verse de l'eau, dans une bouteille bleue.
+papa|Tu sens le sel, Sarah ?
+enfant-f|Oui.
+enfant-f|Ça pique un peu.
+maman|Les chaussures sont encore mouillées.
+narrateur|Raphaël saute sur le chemin de sable.
+narrateur|Ses pieds font toc, toc, toc.
+narrateur|En ce moment, Sarah regarde le jeu, près de la mer.
+narrateur|Un bac à sable.
+narrateur|Un toboggan.
+narrateur|Des balançoires.
+enfant-f|Il court, papa.
+papa|Raphaël a beaucoup d'énergie.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|On va où ?
+maman|Tu choisis, Sarah.
+narrateur|La serviette rayée claque un peu, au vent.
+narrateur|Le chapeau de paille sèche encore.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>oiseau,vague</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1354,7 +1395,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>Trois coins du jeu attendent, près de la mer. Le bac à sable, le toboggan, ou les balançoires ? On peut jouer ou attendre.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1559,9 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|Trois coins du jeu attendent, près de la mer.
+papa|Le bac à sable, le toboggan, ou les balançoires ?
+maman|On peut jouer ou attendre.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers le bac à sable. Un camarade court, saute, creuse. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Lina peut jouer ou attendre. Maman est là. On peut jouer ensemble.</t>
+          <t>Sarah s'agenouille près du bac à sable. Le sable est tiède, un peu rêche. Un grain colle à son genou. Raphaël court, saute, creuse. Le sable vole, tout léger. Il a beaucoup d'énergie. Il saute, maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. Sarah souffle un peu. On creuse ensemble ? Oui ! Un grand trou ! Raphaël creuse très vite. Sarah attend une seconde. Puis elle pose sa pelle, tout doux. Bravo, Sarah. Tu as pu attendre. On peut demander, aussi. Papa, on joue ? Oui. Chacun son tour. Le trou devient rond, tout petit. Une coquille blanche brille au fond.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,10 +1729,37 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Lina va vers le bac à sable. Un camarade court, saute, creuse. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Lina peut jouer ou attendre. Maman est là. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah s'agenouille près du bac à sable.
+narrateur|Le sable est tiède, un peu rêche.
+narrateur|Un grain colle à son genou.
+narrateur|Raphaël court, saute, creuse.
+narrateur|Le sable vole, tout léger.
+narrateur|Il a beaucoup d'énergie.
+enfant-f|Il saute, maman.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+narrateur|Sarah souffle un peu.
+enfant-f|On creuse ensemble ?
+copain|Oui !
+copain|Un grand trou !
+narrateur|Raphaël creuse très vite.
+narrateur|Sarah attend une seconde.
+narrateur|Puis elle pose sa pelle, tout doux.
+maman|Bravo, Sarah.
+maman|Tu as pu attendre.
+papa|On peut demander, aussi.
+enfant-f|Papa, on joue ?
+papa|Oui.
+papa|Chacun son tour.
+narrateur|Le trou devient rond, tout petit.
+narrateur|Une coquille blanche brille au fond.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>sable</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Beaucoup d'énergie, c'est une faute ?</t>
+          <t>Raphaël a de l'énergie. C'est une faute ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1874,7 +1944,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Beaucoup d'énergie, c'est une faute ?</t>
+          <t>narrateur|Raphaël a de l'énergie.
+maman|C'est une faute ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1902,7 +1973,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Lina respire. Maman est là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Sarah respire. Le sable est tiède. On creuse, un peu. Oui. Bravo, Sarah. Tu as fait du bon travail. La coquille blanche reste au fond.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,7 +2117,16 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Lina respire. Maman est là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>papa|Oui.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+narrateur|Sarah respire.
+narrateur|Le sable est tiède.
+enfant-f|On creuse, un peu.
+copain|Oui.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|La coquille blanche reste au fond.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2074,7 +2154,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On peut jouer ou attendre.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2238,7 +2318,9 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On peut jouer ou attendre.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2266,7 +2348,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Au bac, Lina sort les cubes. Le camarade bouge beaucoup. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Sarah sort les cubes de bois. Un cube sent le pin, un peu. Raphaël pose trois cubes, très vite. La tour penche. Il recommence. On attend, un peu ? Encore ! Cette énergie n'est pas une faute. On peut jouer ou attendre. Sarah pose un cube, tout droit. Raphaël souffle. Il attend. Bravo, Raphaël. Tu as attendu. C'est ton tour. Un cube rouge garde un grain de sable. On est encore près de le bac à sable. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,10 +2488,31 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Au bac, Lina sort les cubes. Le camarade bouge beaucoup. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Sarah sort les cubes de bois.
+narrateur|Un cube sent le pin, un peu.
+narrateur|Raphaël pose trois cubes, très vite.
+narrateur|La tour penche.
+narrateur|Il recommence.
+enfant-f|On attend, un peu ?
+copain|Encore !
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+narrateur|Sarah pose un cube, tout droit.
+narrateur|Raphaël souffle.
+narrateur|Il attend.
+papa|Bravo, Raphaël.
+papa|Tu as attendu.
+enfant-f|C'est ton tour.
+narrateur|Un cube rouge garde un grain de sable.
+narrateur|On est encore près de le bac à sable.
+maman|On peut jouer ensemble.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2434,7 +2537,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Une couleur attend, maintenant. Rouge, bleu, ou vert ? Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2602,7 +2705,9 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Une couleur attend, maintenant.
+papa|Rouge, bleu, ou vert ?
+maman|Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2630,7 +2735,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le bac à sable. Puis les cubes. Puis rouge. Un ballon s'immobilise. Lina pose les cubes à sa place. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi rouge. Elle a encore les cubes. On est près de le bac à sable. Sarah pose le cube rouge dans le trou. Il reste droit. Elle pose le cube rouge, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2770,7 +2875,23 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le bac à sable. Puis les cubes. Puis rouge. Un ballon s'immobilise. Lina pose les cubes à sa place. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi rouge.
+narrateur|Elle a encore les cubes.
+narrateur|On est près de le bac à sable.
+narrateur|Sarah pose le cube rouge dans le trou.
+narrateur|Il reste droit.
+narrateur|Elle pose le cube rouge, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2798,7 +2919,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le bac à sable, avec les cubes. Elle a choisi le rouge. Raphaël a eu de l'énergie. Ce n'était pas une faute. La coquille blanche brille encore, au fond du trou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2938,7 +3059,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le bac à sable, avec les cubes.
+narrateur|Elle a choisi le rouge.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La coquille blanche brille encore, au fond du trou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2966,7 +3096,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Lina s'arrête près de bleu. les cubes est rangé. On se tient la main. Lina écoute maman encore une fois. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi bleu. Elle a encore les cubes. On est près de le bac à sable. Le cube bleu a une goutte. Sarah attend. Raphaël pose le sien. Elle pose le cube bleu, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3106,7 +3236,24 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Lina s'arrête près de bleu. les cubes est rangé. On se tient la main. Lina écoute maman encore une fois. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi bleu.
+narrateur|Elle a encore les cubes.
+narrateur|On est près de le bac à sable.
+narrateur|Le cube bleu a une goutte.
+narrateur|Sarah attend.
+narrateur|Raphaël pose le sien.
+narrateur|Elle pose le cube bleu, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3134,7 +3281,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le bac à sable, avec les cubes. Elle a choisi le bleu. Raphaël a eu de l'énergie. Ce n'était pas une faute. La coquille blanche brille encore, au fond du trou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3274,7 +3421,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le bac à sable, avec les cubes.
+narrateur|Elle a choisi le bleu.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La coquille blanche brille encore, au fond du trou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3302,7 +3458,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Lina se souvient de le bac à sable. Et de les cubes. Et de vert. On range un objet. Lina enfile ses chaussons. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi vert. Elle a encore les cubes. On est près de le bac à sable. Un brin d'algue colle au cube vert. Ils rient, tout doux. Elle pose le cube vert, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3442,7 +3598,23 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Lina se souvient de le bac à sable. Et de les cubes. Et de vert. On range un objet. Lina enfile ses chaussons. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi vert.
+narrateur|Elle a encore les cubes.
+narrateur|On est près de le bac à sable.
+narrateur|Un brin d'algue colle au cube vert.
+narrateur|Ils rient, tout doux.
+narrateur|Elle pose le cube vert, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3470,7 +3642,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le bac à sable, avec les cubes. Elle a choisi le vert. Raphaël a eu de l'énergie. Ce n'était pas une faute. La coquille blanche brille encore, au fond du trou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3610,7 +3782,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le bac à sable, avec les cubes.
+narrateur|Elle a choisi le vert.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La coquille blanche brille encore, au fond du trou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3638,7 +3819,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Au bac, Lina ouvre le livre. Le camarade tourne, puis s'assoit. Cette énergie n'est pas une faute. On peut jouer ou attendre. Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Sarah ouvre le livre. La page sent le papier, un peu sec. Raphaël tourne deux pages, trop vite. Puis il s'assoit. Il regarde. On lit ensemble ? Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Sarah montre un bateau, tout bleu. On tourne une page, puis on attend. D'accord. Bravo. Vous lisez, chacun son tour. Le sable poudre un coin de la page. On est encore près de le bac à sable. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3778,11 +3959,30 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Au bac, Lina ouvre le livre. Le camarade tourne, puis s'assoit. Cette énergie n'est pas une faute. On peut jouer ou attendre.
-maman|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Sarah ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Raphaël tourne deux pages, trop vite.
+narrateur|Puis il s'assoit.
+narrateur|Il regarde.
+enfant-f|On lit ensemble ?
+copain|Oui.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+narrateur|Sarah montre un bateau, tout bleu.
+maman|On tourne une page, puis on attend.
+enfant-f|D'accord.
+papa|Bravo.
+papa|Vous lisez, chacun son tour.
+narrateur|Le sable poudre un coin de la page.
+narrateur|On est encore près de le bac à sable.
+maman|On peut jouer ensemble.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3807,7 +4007,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Une couleur attend, maintenant. Rouge, bleu, ou vert ? Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3975,7 +4175,9 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Une couleur attend, maintenant.
+papa|Rouge, bleu, ou vert ?
+maman|Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4003,7 +4205,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec rouge. Après le livre. Près de le bac à sable. Lina s'arrête. Une feuille tombe. Lina boit une gorgée d'eau. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi rouge. Elle a encore le livre. On est près de le bac à sable. Sur la page, un crabe rouge. Raphaël montre, puis attend. Elle pose la page rouge, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4143,7 +4345,23 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec rouge. Après le livre. Près de le bac à sable. Lina s'arrête. Une feuille tombe. Lina boit une gorgée d'eau. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi rouge.
+narrateur|Elle a encore le livre.
+narrateur|On est près de le bac à sable.
+narrateur|Sur la page, un crabe rouge.
+narrateur|Raphaël montre, puis attend.
+narrateur|Elle pose la page rouge, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4171,7 +4389,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le bac à sable, avec le livre. Elle a choisi le rouge. Raphaël a eu de l'énergie. Ce n'était pas une faute. La coquille blanche brille encore, au fond du trou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4311,7 +4529,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le bac à sable, avec le livre.
+narrateur|Elle a choisi le rouge.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La coquille blanche brille encore, au fond du trou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4339,7 +4566,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Lina range le livre. bleu reste près de le bac à sable. Le vent est doux. J'ai appris. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi bleu. Elle a encore le livre. On est près de le bac à sable. La mer du livre est bleue. Sarah tourne, tout lentement. Elle pose la page bleue, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4479,9 +4706,23 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Lina range le livre. bleu reste près de le bac à sable. Le vent est doux.
-enfant-f|J'ai appris. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte.
-narrateur|Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi bleu.
+narrateur|Elle a encore le livre.
+narrateur|On est près de le bac à sable.
+narrateur|La mer du livre est bleue.
+narrateur|Sarah tourne, tout lentement.
+narrateur|Elle pose la page bleue, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4509,7 +4750,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le bac à sable, avec le livre. Elle a choisi le bleu. Raphaël a eu de l'énergie. Ce n'était pas une faute. La coquille blanche brille encore, au fond du trou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4649,7 +4890,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le bac à sable, avec le livre.
+narrateur|Elle a choisi le bleu.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La coquille blanche brille encore, au fond du trou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4677,7 +4927,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Vert est là. le livre aussi. le bac à sable reste dans le souvenir. On attend son tour. Lina tend vert à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi vert. Elle a encore le livre. On est près de le bac à sable. Un bateau vert est dessiné. Ils le regardent, ensemble. Elle pose la page verte, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4817,7 +5067,23 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Vert est là. le livre aussi. le bac à sable reste dans le souvenir. On attend son tour. Lina tend vert à papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi vert.
+narrateur|Elle a encore le livre.
+narrateur|On est près de le bac à sable.
+narrateur|Un bateau vert est dessiné.
+narrateur|Ils le regardent, ensemble.
+narrateur|Elle pose la page verte, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4845,7 +5111,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le bac à sable, avec le livre. Elle a choisi le vert. Raphaël a eu de l'énergie. Ce n'était pas une faute. La coquille blanche brille encore, au fond du trou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4985,7 +5251,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le bac à sable, avec le livre.
+narrateur|Elle a choisi le vert.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La coquille blanche brille encore, au fond du trou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5013,7 +5288,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Au bac, Lina sort la dînette. Le camarade sert très vite. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Sarah sort la dînette. Une petite assiette sonne, tout creux. Raphaël sert très vite, trop vite. L'eau imaginaire déborde, un peu. Maman, on fait comment ? On peut jouer ou attendre. Cette énergie n'est pas une faute. Sarah pose la tasse, tout doux. Encore du thé ? Après toi. Bravo, Sarah. Tu as attendu. Une petite cuillère brille au soleil. Une tasse miniature a du sable au bord. On est encore près de le bac à sable. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5153,10 +5428,29 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Au bac, Lina sort la dînette. Le camarade sert très vite. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Sarah sort la dînette.
+narrateur|Une petite assiette sonne, tout creux.
+narrateur|Raphaël sert très vite, trop vite.
+narrateur|L'eau imaginaire déborde, un peu.
+enfant-f|Maman, on fait comment ?
+maman|On peut jouer ou attendre.
+papa|Cette énergie n'est pas une faute.
+narrateur|Sarah pose la tasse, tout doux.
+copain|Encore du thé ?
+enfant-f|Après toi.
+papa|Bravo, Sarah.
+papa|Tu as attendu.
+narrateur|Une petite cuillère brille au soleil.
+narrateur|Une tasse miniature a du sable au bord.
+narrateur|On est encore près de le bac à sable.
+maman|On peut jouer ensemble.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,7 +5475,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Une couleur attend, maintenant. Rouge, bleu, ou vert ? Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5349,7 +5643,9 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Une couleur attend, maintenant.
+papa|Rouge, bleu, ou vert ?
+maman|Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5377,7 +5673,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint rouge. la dînette est rangé. le bac à sable est fini. Le savon sent bon. Lina sourit. Maman sourit aussi. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi rouge. Elle a encore la dînette. On est près de le bac à sable. Sarah sert dans la tasse rouge. Raphaël attend sa gorgée. Elle pose la tasse rouge, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5517,7 +5813,23 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint rouge. la dînette est rangé. le bac à sable est fini. Le savon sent bon. Lina sourit. Maman sourit aussi. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi rouge.
+narrateur|Elle a encore la dînette.
+narrateur|On est près de le bac à sable.
+narrateur|Sarah sert dans la tasse rouge.
+narrateur|Raphaël attend sa gorgée.
+narrateur|Elle pose la tasse rouge, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5545,7 +5857,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le bac à sable, avec la dînette. Elle a choisi le rouge. Raphaël a eu de l'énergie. Ce n'était pas une faute. La coquille blanche brille encore, au fond du trou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5685,7 +5997,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le bac à sable, avec la dînette.
+narrateur|Elle a choisi le rouge.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La coquille blanche brille encore, au fond du trou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5713,7 +6034,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de bleu. Lina pose la dînette. le bac à sable est derrière. On dit merci. Lina range la tasse. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi bleu. Elle a encore la dînette. On est près de le bac à sable. L'assiette bleue sent le sel. Ils font un pique-nique. Elle pose l'assiette bleue, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5853,7 +6174,23 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de bleu. Lina pose la dînette. le bac à sable est derrière. On dit merci. Lina range la tasse. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi bleu.
+narrateur|Elle a encore la dînette.
+narrateur|On est près de le bac à sable.
+narrateur|L'assiette bleue sent le sel.
+narrateur|Ils font un pique-nique.
+narrateur|Elle pose l'assiette bleue, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5881,7 +6218,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le bac à sable, avec la dînette. Elle a choisi le bleu. Raphaël a eu de l'énergie. Ce n'était pas une faute. La coquille blanche brille encore, au fond du trou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6021,7 +6358,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le bac à sable, avec la dînette.
+narrateur|Elle a choisi le bleu.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La coquille blanche brille encore, au fond du trou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6049,7 +6395,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Lina montre vert. Maman a vu le bac à sable. Et la dînette. Un crochet tient bien le manteau. Lina répète tout bas le geste. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi vert. Elle a encore la dînette. On est près de le bac à sable. La cuillère verte a du sable. Sarah l'essuie, tout doux. Elle pose la cuillère verte, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6189,7 +6535,23 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Lina montre vert. Maman a vu le bac à sable. Et la dînette. Un crochet tient bien le manteau. Lina répète tout bas le geste. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi vert.
+narrateur|Elle a encore la dînette.
+narrateur|On est près de le bac à sable.
+narrateur|La cuillère verte a du sable.
+narrateur|Sarah l'essuie, tout doux.
+narrateur|Elle pose la cuillère verte, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6217,7 +6579,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le bac à sable, avec la dînette. Elle a choisi le vert. Raphaël a eu de l'énergie. Ce n'était pas une faute. La coquille blanche brille encore, au fond du trou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6357,7 +6719,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le bac à sable, avec la dînette.
+narrateur|Elle a choisi le vert.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La coquille blanche brille encore, au fond du trou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6385,7 +6756,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers le toboggan. Un camarade monte, descend, recommence. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Lina peut jouer ou attendre. Papa porte le sac. On peut jouer ensemble.</t>
+          <t>Sarah pose la main sur le toboggan. Le bois est chaud, un peu lisse. Une marche sonne, tout creux. Raphaël monte, descend, recommence. Il a beaucoup d'énergie. Encore, papa. Cette énergie n'est pas une faute. On peut jouer ou attendre. Sarah reste en bas, un moment. J'attends mon tour. Bravo. Tu as attendu. Raphaël arrive, tout vite. Il souffle. Il rit. À toi ! Sarah monte, tout doux. Le vent sent le sel, sur la joue. On peut demander à un adulte. Tu me regardes, papa ? Oui. Je te vois. Sarah glisse. Le bois est tiède. Raphaël attend, un tout petit peu.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6525,7 +6896,31 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Lina va vers le toboggan. Un camarade monte, descend, recommence. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Lina peut jouer ou attendre. Papa porte le sac. On peut jouer ensemble.</t>
+          <t>narrateur|Sarah pose la main sur le toboggan.
+narrateur|Le bois est chaud, un peu lisse.
+narrateur|Une marche sonne, tout creux.
+narrateur|Raphaël monte, descend, recommence.
+narrateur|Il a beaucoup d'énergie.
+enfant-f|Encore, papa.
+papa|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+narrateur|Sarah reste en bas, un moment.
+enfant-f|J'attends mon tour.
+maman|Bravo.
+maman|Tu as attendu.
+narrateur|Raphaël arrive, tout vite.
+narrateur|Il souffle.
+narrateur|Il rit.
+copain|À toi !
+narrateur|Sarah monte, tout doux.
+narrateur|Le vent sent le sel, sur la joue.
+papa|On peut demander à un adulte.
+enfant-f|Tu me regardes, papa ?
+papa|Oui.
+papa|Je te vois.
+narrateur|Sarah glisse.
+narrateur|Le bois est tiède.
+narrateur|Raphaël attend, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6553,7 +6948,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>On joue, ou on attend ?</t>
+          <t>Raphaël recommence. On joue, ou on attend ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6709,7 +7104,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|On joue, ou on attend ?</t>
+          <t>narrateur|Raphaël recommence.
+papa|On joue, ou on attend ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6737,7 +7133,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Lina retient le geste. Maman sourit. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Oui. On peut jouer ou attendre. Cette énergie n'est pas une faute. Sarah retient le geste, tout doux. J'attends. Après, c'est toi. Bravo. C'est du bon travail. Le bois du toboggan reste chaud.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6881,7 +7277,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Lina retient le geste. Maman sourit. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>maman|Oui.
+maman|On peut jouer ou attendre.
+papa|Cette énergie n'est pas une faute.
+narrateur|Sarah retient le geste, tout doux.
+enfant-f|J'attends.
+copain|Après, c'est toi.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Le bois du toboggan reste chaud.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6909,7 +7313,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On peut jouer ou attendre.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7073,7 +7477,9 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On peut jouer ou attendre.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7101,7 +7507,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Au toboggan, Lina a les cubes. Le camarade monte encore. Cette énergie n'est pas une faute. On peut jouer ou attendre. Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Sarah sort les cubes de bois. Un cube sent le pin, un peu. Raphaël pose trois cubes, très vite. La tour penche. Il recommence. On attend, un peu ? Encore ! Cette énergie n'est pas une faute. On peut jouer ou attendre. Sarah pose un cube, tout droit. Raphaël souffle. Il attend. Bravo, Raphaël. Tu as attendu. C'est ton tour. Un cube tapote la marche du toboggan. On est encore près de le toboggan. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7241,11 +7647,31 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Au toboggan, Lina a les cubes. Le camarade monte encore. Cette énergie n'est pas une faute. On peut jouer ou attendre.
-maman|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Sarah sort les cubes de bois.
+narrateur|Un cube sent le pin, un peu.
+narrateur|Raphaël pose trois cubes, très vite.
+narrateur|La tour penche.
+narrateur|Il recommence.
+enfant-f|On attend, un peu ?
+copain|Encore !
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+narrateur|Sarah pose un cube, tout droit.
+narrateur|Raphaël souffle.
+narrateur|Il attend.
+papa|Bravo, Raphaël.
+papa|Tu as attendu.
+enfant-f|C'est ton tour.
+narrateur|Un cube tapote la marche du toboggan.
+narrateur|On est encore près de le toboggan.
+maman|On peut jouer ensemble.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7270,7 +7696,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Une couleur attend, maintenant. Rouge, bleu, ou vert ? Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7438,7 +7864,9 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Une couleur attend, maintenant.
+papa|Rouge, bleu, ou vert ?
+maman|Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7466,7 +7894,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le toboggan. Puis les cubes. Puis rouge. Ça sent le pain chaud. Lina montre rouge à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi rouge. Elle a encore les cubes. On est près de le toboggan. Le cube rouge attend en bas. Raphaël glisse, puis le pose. Elle pose le cube rouge, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7606,7 +8034,23 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le toboggan. Puis les cubes. Puis rouge. Ça sent le pain chaud. Lina montre rouge à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi rouge.
+narrateur|Elle a encore les cubes.
+narrateur|On est près de le toboggan.
+narrateur|Le cube rouge attend en bas.
+narrateur|Raphaël glisse, puis le pose.
+narrateur|Elle pose le cube rouge, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7634,7 +8078,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le toboggan, avec les cubes. Elle a choisi le rouge. Raphaël a eu de l'énergie. Ce n'était pas une faute. Le bois du toboggan reste chaud, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7774,7 +8218,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le toboggan, avec les cubes.
+narrateur|Elle a choisi le rouge.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|Le bois du toboggan reste chaud, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7802,7 +8255,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Lina s'arrête près de bleu. les cubes est rangé. Un ruban reste dans la poche. Lina pose sa tête un moment. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi bleu. Elle a encore les cubes. On est près de le toboggan. Sarah garde le cube bleu. Elle attend son tour, en haut. Elle pose le cube bleu, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7942,7 +8395,23 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Lina s'arrête près de bleu. les cubes est rangé. Un ruban reste dans la poche. Lina pose sa tête un moment. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi bleu.
+narrateur|Elle a encore les cubes.
+narrateur|On est près de le toboggan.
+narrateur|Sarah garde le cube bleu.
+narrateur|Elle attend son tour, en haut.
+narrateur|Elle pose le cube bleu, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7970,7 +8439,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le toboggan, avec les cubes. Elle a choisi le bleu. Raphaël a eu de l'énergie. Ce n'était pas une faute. Le bois du toboggan reste chaud, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8110,7 +8579,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le toboggan, avec les cubes.
+narrateur|Elle a choisi le bleu.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|Le bois du toboggan reste chaud, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8138,7 +8616,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Lina se souvient de le toboggan. Et de les cubes. Et de vert. Le sol est un peu froid. Lina marche près de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi vert. Elle a encore les cubes. On est près de le toboggan. Le cube vert roule d'une marche. Ils le ramassent, ensemble. Elle pose le cube vert, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8278,7 +8756,23 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Lina se souvient de le toboggan. Et de les cubes. Et de vert. Le sol est un peu froid. Lina marche près de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi vert.
+narrateur|Elle a encore les cubes.
+narrateur|On est près de le toboggan.
+narrateur|Le cube vert roule d'une marche.
+narrateur|Ils le ramassent, ensemble.
+narrateur|Elle pose le cube vert, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8306,7 +8800,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le toboggan, avec les cubes. Elle a choisi le vert. Raphaël a eu de l'énergie. Ce n'était pas une faute. Le bois du toboggan reste chaud, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8446,7 +8940,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le toboggan, avec les cubes.
+narrateur|Elle a choisi le vert.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|Le bois du toboggan reste chaud, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8474,7 +8977,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Au toboggan, Lina a le livre. Le camarade attend une seconde. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Sarah ouvre le livre. La page sent le papier, un peu sec. Raphaël tourne deux pages, trop vite. Puis il s'assoit. Il regarde. On lit ensemble ? Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Sarah montre un bateau, tout bleu. On tourne une page, puis on attend. D'accord. Bravo. Vous lisez, chacun son tour. Le vent tourne une page, tout seul. On est encore près de le toboggan. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8614,10 +9117,30 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Au toboggan, Lina a le livre. Le camarade attend une seconde. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Sarah ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Raphaël tourne deux pages, trop vite.
+narrateur|Puis il s'assoit.
+narrateur|Il regarde.
+enfant-f|On lit ensemble ?
+copain|Oui.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+narrateur|Sarah montre un bateau, tout bleu.
+maman|On tourne une page, puis on attend.
+enfant-f|D'accord.
+papa|Bravo.
+papa|Vous lisez, chacun son tour.
+narrateur|Le vent tourne une page, tout seul.
+narrateur|On est encore près de le toboggan.
+maman|On peut jouer ensemble.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8642,7 +9165,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Une couleur attend, maintenant. Rouge, bleu, ou vert ? Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8810,7 +9333,9 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Une couleur attend, maintenant.
+papa|Rouge, bleu, ou vert ?
+maman|Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8838,7 +9363,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec rouge. Après le livre. Près de le toboggan. Lina s'arrête. On écoute jusqu'au bout. Lina souffle, puis sourit à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi rouge. Elle a encore le livre. On est près de le toboggan. La couverture rouge est chaude. Ils lisent après la glissade. Elle pose la page rouge, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8978,7 +9503,23 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec rouge. Après le livre. Près de le toboggan. Lina s'arrête. On écoute jusqu'au bout. Lina souffle, puis sourit à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi rouge.
+narrateur|Elle a encore le livre.
+narrateur|On est près de le toboggan.
+narrateur|La couverture rouge est chaude.
+narrateur|Ils lisent après la glissade.
+narrateur|Elle pose la page rouge, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9006,7 +9547,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le toboggan, avec le livre. Elle a choisi le rouge. Raphaël a eu de l'énergie. Ce n'était pas une faute. Le bois du toboggan reste chaud, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9146,7 +9687,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le toboggan, avec le livre.
+narrateur|Elle a choisi le rouge.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|Le bois du toboggan reste chaud, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9174,7 +9724,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Lina range le livre. bleu reste près de le toboggan. Une cloche tinte, tout loin. Lina s'assoit près de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi bleu. Elle a encore le livre. On est près de le toboggan. Une vague bleue est sur la page. Sarah montre. Raphaël écoute. Elle pose la page bleue, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9314,7 +9864,24 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Lina range le livre. bleu reste près de le toboggan. Une cloche tinte, tout loin. Lina s'assoit près de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi bleu.
+narrateur|Elle a encore le livre.
+narrateur|On est près de le toboggan.
+narrateur|Une vague bleue est sur la page.
+narrateur|Sarah montre.
+narrateur|Raphaël écoute.
+narrateur|Elle pose la page bleue, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9342,7 +9909,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le toboggan, avec le livre. Elle a choisi le bleu. Raphaël a eu de l'énergie. Ce n'était pas une faute. Le bois du toboggan reste chaud, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9482,7 +10049,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le toboggan, avec le livre.
+narrateur|Elle a choisi le bleu.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|Le bois du toboggan reste chaud, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9510,7 +10086,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Vert est là. le livre aussi. le toboggan reste dans le souvenir. Il y a des miettes sur la table. Lina ferme le sac. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi vert. Elle a encore le livre. On est près de le toboggan. Une île verte est dessinée. Ils soufflent, puis lisent. Elle pose la page verte, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9650,7 +10226,23 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Vert est là. le livre aussi. le toboggan reste dans le souvenir. Il y a des miettes sur la table. Lina ferme le sac. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi vert.
+narrateur|Elle a encore le livre.
+narrateur|On est près de le toboggan.
+narrateur|Une île verte est dessinée.
+narrateur|Ils soufflent, puis lisent.
+narrateur|Elle pose la page verte, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9678,7 +10270,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le toboggan, avec le livre. Elle a choisi le vert. Raphaël a eu de l'énergie. Ce n'était pas une faute. Le bois du toboggan reste chaud, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9818,7 +10410,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le toboggan, avec le livre.
+narrateur|Elle a choisi le vert.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|Le bois du toboggan reste chaud, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9846,7 +10447,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Au toboggan, Lina a la dînette. Le camarade rit. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Sarah sort la dînette. Une petite assiette sonne, tout creux. Raphaël sert très vite, trop vite. L'eau imaginaire déborde, un peu. Maman, on fait comment ? On peut jouer ou attendre. Cette énergie n'est pas une faute. Sarah pose la tasse, tout doux. Encore du thé ? Après toi. Bravo, Sarah. Tu as attendu. Une petite cuillère brille au soleil. La petite casserole est au pied du toboggan. On est encore près de le toboggan. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9986,10 +10587,29 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Au toboggan, Lina a la dînette. Le camarade rit. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Sarah sort la dînette.
+narrateur|Une petite assiette sonne, tout creux.
+narrateur|Raphaël sert très vite, trop vite.
+narrateur|L'eau imaginaire déborde, un peu.
+enfant-f|Maman, on fait comment ?
+maman|On peut jouer ou attendre.
+papa|Cette énergie n'est pas une faute.
+narrateur|Sarah pose la tasse, tout doux.
+copain|Encore du thé ?
+enfant-f|Après toi.
+papa|Bravo, Sarah.
+papa|Tu as attendu.
+narrateur|Une petite cuillère brille au soleil.
+narrateur|La petite casserole est au pied du toboggan.
+narrateur|On est encore près de le toboggan.
+maman|On peut jouer ensemble.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10014,7 +10634,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Une couleur attend, maintenant. Rouge, bleu, ou vert ? Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10182,7 +10802,9 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Une couleur attend, maintenant.
+papa|Rouge, bleu, ou vert ?
+maman|Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10210,7 +10832,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint rouge. la dînette est rangé. le toboggan est fini. L'eau coule, tout petit bruit. Lina ferme la porte, tout doux. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi rouge. Elle a encore la dînette. On est près de le toboggan. La tasse rouge est au pied. Après la glissade, on sert. Elle pose la tasse rouge, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10350,7 +10972,23 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint rouge. la dînette est rangé. le toboggan est fini. L'eau coule, tout petit bruit. Lina ferme la porte, tout doux. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi rouge.
+narrateur|Elle a encore la dînette.
+narrateur|On est près de le toboggan.
+narrateur|La tasse rouge est au pied.
+narrateur|Après la glissade, on sert.
+narrateur|Elle pose la tasse rouge, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10378,7 +11016,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le toboggan, avec la dînette. Elle a choisi le rouge. Raphaël a eu de l'énergie. Ce n'était pas une faute. Le bois du toboggan reste chaud, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10518,7 +11156,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le toboggan, avec la dînette.
+narrateur|Elle a choisi le rouge.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|Le bois du toboggan reste chaud, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10546,7 +11193,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de bleu. Lina pose la dînette. le toboggan est derrière. La couverture est douce. Lina prend la main de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi bleu. Elle a encore la dînette. On est près de le toboggan. L'assiette bleue est tiède. Sarah attend. Raphaël s'assoit. Elle pose l'assiette bleue, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10686,7 +11333,24 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de bleu. Lina pose la dînette. le toboggan est derrière. La couverture est douce. Lina prend la main de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi bleu.
+narrateur|Elle a encore la dînette.
+narrateur|On est près de le toboggan.
+narrateur|L'assiette bleue est tiède.
+narrateur|Sarah attend.
+narrateur|Raphaël s'assoit.
+narrateur|Elle pose l'assiette bleue, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10714,7 +11378,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le toboggan, avec la dînette. Elle a choisi le bleu. Raphaël a eu de l'énergie. Ce n'était pas une faute. Le bois du toboggan reste chaud, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10854,7 +11518,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le toboggan, avec la dînette.
+narrateur|Elle a choisi le bleu.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|Le bois du toboggan reste chaud, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10882,7 +11555,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Lina montre vert. Maman a vu le toboggan. Et la dînette. Une tasse cliquette. Lina serre la main de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi vert. Elle a encore la dînette. On est près de le toboggan. La cuillère verte tinte. Ils font la soupe, tout calmes. Elle pose la cuillère verte, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11022,7 +11695,23 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Lina montre vert. Maman a vu le toboggan. Et la dînette. Une tasse cliquette. Lina serre la main de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi vert.
+narrateur|Elle a encore la dînette.
+narrateur|On est près de le toboggan.
+narrateur|La cuillère verte tinte.
+narrateur|Ils font la soupe, tout calmes.
+narrateur|Elle pose la cuillère verte, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11050,7 +11739,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu le toboggan, avec la dînette. Elle a choisi le vert. Raphaël a eu de l'énergie. Ce n'était pas une faute. Le bois du toboggan reste chaud, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11190,7 +11879,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu le toboggan, avec la dînette.
+narrateur|Elle a choisi le vert.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|Le bois du toboggan reste chaud, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11218,7 +11916,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers les balançoires. Un camarade pousse fort, puis rit. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Lina peut jouer ou attendre. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Sarah s'approche des balançoires. La chaîne est froide, un peu sablée. Elle fait un tout petit criiii. Raphaël pousse fort, puis rit. Il a beaucoup d'énergie. Il va haut, maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Sarah pose les deux pieds au sol. Papa, je m'assois à côté ? Oui. Doucement, comme ça. Sarah s'assoit. La planche est chaude. On se balance ! Raphaël va vite. Sarah va lentement. Chacun son rythme. On peut jouer ensemble. D'accord. Bravo, Sarah. Tu as demandé. Une mouette passe, tout loin. La chaîne chante encore, tout bas.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11358,7 +12056,31 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Lina va vers les balançoires. Un camarade pousse fort, puis rit. Il a beaucoup d'énergie. Cette énergie n'est pas une faute. Lina peut jouer ou attendre. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Sarah s'approche des balançoires.
+narrateur|La chaîne est froide, un peu sablée.
+narrateur|Elle fait un tout petit criiii.
+narrateur|Raphaël pousse fort, puis rit.
+narrateur|Il a beaucoup d'énergie.
+enfant-f|Il va haut, maman.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+narrateur|Sarah pose les deux pieds au sol.
+enfant-f|Papa, je m'assois à côté ?
+papa|Oui.
+papa|Doucement, comme ça.
+narrateur|Sarah s'assoit.
+narrateur|La planche est chaude.
+copain|On se balance !
+narrateur|Raphaël va vite.
+narrateur|Sarah va lentement.
+maman|Chacun son rythme.
+maman|On peut jouer ensemble.
+enfant-f|D'accord.
+papa|Bravo, Sarah.
+papa|Tu as demandé.
+narrateur|Une mouette passe, tout loin.
+narrateur|La chaîne chante encore, tout bas.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11386,7 +12108,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>On demande à un adulte ?</t>
+          <t>Sarah veut s'asseoir. On demande à un adulte ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11542,7 +12264,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|On demande à un adulte ?</t>
+          <t>narrateur|Sarah veut s'asseoir.
+maman|On demande à un adulte ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11570,7 +12293,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Lina hoche la tête. On continue, avec maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Oui. On peut demander à un adulte. Cette énergie n'est pas une faute. On peut jouer ou attendre. Sarah hoche la tête. Merci, papa. Bravo. Tu as demandé. La chaîne se tait, un moment.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11714,7 +12437,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Lina hoche la tête. On continue, avec maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>papa|Oui.
+papa|On peut demander à un adulte.
+maman|Cette énergie n'est pas une faute.
+maman|On peut jouer ou attendre.
+narrateur|Sarah hoche la tête.
+enfant-f|Merci, papa.
+papa|Bravo.
+papa|Tu as demandé.
+narrateur|La chaîne se tait, un moment.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11742,7 +12473,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On peut jouer ou attendre.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11906,7 +12637,9 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On peut jouer ou attendre.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11934,7 +12667,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Aux balançoires, Lina a les cubes. Le camarade pousse. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Sarah sort les cubes de bois. Un cube sent le pin, un peu. Raphaël pose trois cubes, très vite. La tour penche. Il recommence. On attend, un peu ? Encore ! Cette énergie n'est pas une faute. On peut jouer ou attendre. Sarah pose un cube, tout droit. Raphaël souffle. Il attend. Bravo, Raphaël. Tu as attendu. C'est ton tour. Un cube repose près de la chaîne. On est encore près de les balançoires. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12074,10 +12807,31 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Aux balançoires, Lina a les cubes. Le camarade pousse. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman reste tout près. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Sarah sort les cubes de bois.
+narrateur|Un cube sent le pin, un peu.
+narrateur|Raphaël pose trois cubes, très vite.
+narrateur|La tour penche.
+narrateur|Il recommence.
+enfant-f|On attend, un peu ?
+copain|Encore !
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+narrateur|Sarah pose un cube, tout droit.
+narrateur|Raphaël souffle.
+narrateur|Il attend.
+papa|Bravo, Raphaël.
+papa|Tu as attendu.
+enfant-f|C'est ton tour.
+narrateur|Un cube repose près de la chaîne.
+narrateur|On est encore près de les balançoires.
+maman|On peut jouer ensemble.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12102,7 +12856,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Une couleur attend, maintenant. Rouge, bleu, ou vert ? Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12270,7 +13024,9 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Une couleur attend, maintenant.
+papa|Rouge, bleu, ou vert ?
+maman|Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12298,7 +13054,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi les balançoires. Puis les cubes. Puis rouge. Un linge sèche à l'air. Lina dit merci à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi rouge. Elle a encore les cubes. On est près de les balançoires. Sarah tient le cube rouge. La balançoire s'arrête. On pose. Elle pose le cube rouge, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12438,7 +13194,24 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi les balançoires. Puis les cubes. Puis rouge. Un linge sèche à l'air. Lina dit merci à maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi rouge.
+narrateur|Elle a encore les cubes.
+narrateur|On est près de les balançoires.
+narrateur|Sarah tient le cube rouge.
+narrateur|La balançoire s'arrête.
+narrateur|On pose.
+narrateur|Elle pose le cube rouge, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12466,7 +13239,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu les balançoires, avec les cubes. Elle a choisi le rouge. Raphaël a eu de l'énergie. Ce n'était pas une faute. La chaîne des balançoires se tait, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12606,7 +13379,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu les balançoires, avec les cubes.
+narrateur|Elle a choisi le rouge.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La chaîne des balançoires se tait, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12634,7 +13416,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Lina s'arrête près de bleu. les cubes est rangé. Un chat miaule une fois. Lina plie un pull. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi bleu. Elle a encore les cubes. On est près de les balançoires. Le cube bleu est dans sa poche. Raphaël attend, les pieds au sol. Elle pose le cube bleu, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12774,7 +13556,23 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Lina s'arrête près de bleu. les cubes est rangé. Un chat miaule une fois. Lina plie un pull. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi bleu.
+narrateur|Elle a encore les cubes.
+narrateur|On est près de les balançoires.
+narrateur|Le cube bleu est dans sa poche.
+narrateur|Raphaël attend, les pieds au sol.
+narrateur|Elle pose le cube bleu, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12802,7 +13600,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu les balançoires, avec les cubes. Elle a choisi le bleu. Raphaël a eu de l'énergie. Ce n'était pas une faute. La chaîne des balançoires se tait, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12942,7 +13740,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu les balançoires, avec les cubes.
+narrateur|Elle a choisi le bleu.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La chaîne des balançoires se tait, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12970,7 +13777,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Lina se souvient de les balançoires. Et de les cubes. Et de vert. Une chaussette est encore sablée. Papa n'est pas loin. Lina les rejoint. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi vert. Elle a encore les cubes. On est près de les balançoires. Le cube vert brille. Ils le posent entre les deux sièges. Elle pose le cube vert, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13110,7 +13917,23 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Lina se souvient de les balançoires. Et de les cubes. Et de vert. Une chaussette est encore sablée. Papa n'est pas loin. Lina les rejoint. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi vert.
+narrateur|Elle a encore les cubes.
+narrateur|On est près de les balançoires.
+narrateur|Le cube vert brille.
+narrateur|Ils le posent entre les deux sièges.
+narrateur|Elle pose le cube vert, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13138,7 +13961,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu les balançoires, avec les cubes. Elle a choisi le vert. Raphaël a eu de l'énergie. Ce n'était pas une faute. La chaîne des balançoires se tait, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13278,7 +14101,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu les balançoires, avec les cubes.
+narrateur|Elle a choisi le vert.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La chaîne des balançoires se tait, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13306,7 +14138,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Aux balançoires, Lina a le livre. Le camarade s'assoit. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Sarah ouvre le livre. La page sent le papier, un peu sec. Raphaël tourne deux pages, trop vite. Puis il s'assoit. Il regarde. On lit ensemble ? Oui. Cette énergie n'est pas une faute. On peut jouer ou attendre. Sarah montre un bateau, tout bleu. On tourne une page, puis on attend. D'accord. Bravo. Vous lisez, chacun son tour. Le livre est ouvert, sous la balançoire. On est encore près de les balançoires. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13446,10 +14278,30 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Aux balançoires, Lina a le livre. Le camarade s'assoit. Cette énergie n'est pas une faute. On peut jouer ou attendre. Maman montre le geste, lentement. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Sarah ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Raphaël tourne deux pages, trop vite.
+narrateur|Puis il s'assoit.
+narrateur|Il regarde.
+enfant-f|On lit ensemble ?
+copain|Oui.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+narrateur|Sarah montre un bateau, tout bleu.
+maman|On tourne une page, puis on attend.
+enfant-f|D'accord.
+papa|Bravo.
+papa|Vous lisez, chacun son tour.
+narrateur|Le livre est ouvert, sous la balançoire.
+narrateur|On est encore près de les balançoires.
+maman|On peut jouer ensemble.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13474,7 +14326,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Une couleur attend, maintenant. Rouge, bleu, ou vert ? Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13642,7 +14494,9 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Une couleur attend, maintenant.
+papa|Rouge, bleu, ou vert ?
+maman|Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13670,7 +14524,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec rouge. Après le livre. Près de les balançoires. Lina s'arrête. Un vélo passe au loin. Lina caresse le doudou. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi rouge. Elle a encore le livre. On est près de les balançoires. Le livre rouge est sur les genoux. On se balance, tout lent. Elle pose la page rouge, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13810,7 +14664,23 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec rouge. Après le livre. Près de les balançoires. Lina s'arrête. Un vélo passe au loin. Lina caresse le doudou. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi rouge.
+narrateur|Elle a encore le livre.
+narrateur|On est près de les balançoires.
+narrateur|Le livre rouge est sur les genoux.
+narrateur|On se balance, tout lent.
+narrateur|Elle pose la page rouge, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13838,7 +14708,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu les balançoires, avec le livre. Elle a choisi le rouge. Raphaël a eu de l'énergie. Ce n'était pas une faute. La chaîne des balançoires se tait, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13978,7 +14848,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu les balançoires, avec le livre.
+narrateur|Elle a choisi le rouge.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La chaîne des balançoires se tait, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14006,7 +14885,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Lina range le livre. bleu reste près de les balançoires. Les chaussures font toc toc. Lina range les balançoires dans sa tête, comme un souvenir. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi bleu. Elle a encore le livre. On est près de les balançoires. La page bleue claque un peu. Sarah attend. Raphaël écoute. Elle pose la page bleue, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14146,7 +15025,24 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Lina range le livre. bleu reste près de les balançoires. Les chaussures font toc toc. Lina range les balançoires dans sa tête, comme un souvenir. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi bleu.
+narrateur|Elle a encore le livre.
+narrateur|On est près de les balançoires.
+narrateur|La page bleue claque un peu.
+narrateur|Sarah attend.
+narrateur|Raphaël écoute.
+narrateur|Elle pose la page bleue, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14174,7 +15070,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu les balançoires, avec le livre. Elle a choisi le bleu. Raphaël a eu de l'énergie. Ce n'était pas une faute. La chaîne des balançoires se tait, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14314,7 +15210,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu les balançoires, avec le livre.
+narrateur|Elle a choisi le bleu.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La chaîne des balançoires se tait, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14342,7 +15247,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Vert est là. le livre aussi. les balançoires reste dans le souvenir. On entend un oiseau. Lina raccroche un linge. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi vert. Elle a encore le livre. On est près de les balançoires. Une feuille verte est collée. Ils la gardent, comme un secret. Elle pose la page verte, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14482,7 +15387,23 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Vert est là. le livre aussi. les balançoires reste dans le souvenir. On entend un oiseau. Lina raccroche un linge. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi vert.
+narrateur|Elle a encore le livre.
+narrateur|On est près de les balançoires.
+narrateur|Une feuille verte est collée.
+narrateur|Ils la gardent, comme un secret.
+narrateur|Elle pose la page verte, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14510,7 +15431,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu les balançoires, avec le livre. Elle a choisi le vert. Raphaël a eu de l'énergie. Ce n'était pas une faute. La chaîne des balançoires se tait, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14650,7 +15571,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu les balançoires, avec le livre.
+narrateur|Elle a choisi le vert.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La chaîne des balançoires se tait, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14678,7 +15608,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Aux balançoires, Lina a la dînette. Le camarade souffle. Cette énergie n'est pas une faute. On peut jouer ou attendre. Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
+          <t>Sarah sort la dînette. Une petite assiette sonne, tout creux. Raphaël sert très vite, trop vite. L'eau imaginaire déborde, un peu. Maman, on fait comment ? On peut jouer ou attendre. Cette énergie n'est pas une faute. Sarah pose la tasse, tout doux. Encore du thé ? Après toi. Bravo, Sarah. Tu as attendu. Une petite cuillère brille au soleil. Une cuillère miniature tinte près du pied. On est encore près de les balançoires. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14818,11 +15748,29 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Aux balançoires, Lina a la dînette. Le camarade souffle. Cette énergie n'est pas une faute. On peut jouer ou attendre.
-maman|Je suis là. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Sarah sort la dînette.
+narrateur|Une petite assiette sonne, tout creux.
+narrateur|Raphaël sert très vite, trop vite.
+narrateur|L'eau imaginaire déborde, un peu.
+enfant-f|Maman, on fait comment ?
+maman|On peut jouer ou attendre.
+papa|Cette énergie n'est pas une faute.
+narrateur|Sarah pose la tasse, tout doux.
+copain|Encore du thé ?
+enfant-f|Après toi.
+papa|Bravo, Sarah.
+papa|Tu as attendu.
+narrateur|Une petite cuillère brille au soleil.
+narrateur|Une cuillère miniature tinte près du pied.
+narrateur|On est encore près de les balançoires.
+maman|On peut jouer ensemble.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14847,7 +15795,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Une couleur attend, maintenant. Rouge, bleu, ou vert ? Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15015,7 +15963,9 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Une couleur attend, maintenant.
+papa|Rouge, bleu, ou vert ?
+maman|Cette énergie n'est pas une faute.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15043,7 +15993,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint rouge. la dînette est rangé. les balançoires est fini. On souffle doucement. Lina chuchote : c'est fini. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi rouge. Elle a encore la dînette. On est près de les balançoires. La tasse rouge est dans l'herbe. Après, on sert, tout doux. Elle pose la tasse rouge, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15183,7 +16133,23 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint rouge. la dînette est rangé. les balançoires est fini. On souffle doucement. Lina chuchote : c'est fini. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi rouge.
+narrateur|Elle a encore la dînette.
+narrateur|On est près de les balançoires.
+narrateur|La tasse rouge est dans l'herbe.
+narrateur|Après, on sert, tout doux.
+narrateur|Elle pose la tasse rouge, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15211,7 +16177,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu les balançoires, avec la dînette. Elle a choisi le rouge. Raphaël a eu de l'énergie. Ce n'était pas une faute. La chaîne des balançoires se tait, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15351,7 +16317,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu les balançoires, avec la dînette.
+narrateur|Elle a choisi le rouge.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La chaîne des balançoires se tait, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15379,7 +16354,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de bleu. Lina pose la dînette. les balançoires est derrière. Une pomme brille un peu. Lina range encore un peu, près de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi bleu. Elle a encore la dînette. On est près de les balançoires. L'assiette bleue reste près des pieds. Raphaël souffle, puis attend. Elle pose l'assiette bleue, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15519,7 +16494,23 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de bleu. Lina pose la dînette. les balançoires est derrière. Une pomme brille un peu. Lina range encore un peu, près de maman. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi bleu.
+narrateur|Elle a encore la dînette.
+narrateur|On est près de les balançoires.
+narrateur|L'assiette bleue reste près des pieds.
+narrateur|Raphaël souffle, puis attend.
+narrateur|Elle pose l'assiette bleue, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15547,7 +16538,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu les balançoires, avec la dînette. Elle a choisi le bleu. Raphaël a eu de l'énergie. Ce n'était pas une faute. La chaîne des balançoires se tait, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15687,7 +16678,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu les balançoires, avec la dînette.
+narrateur|Elle a choisi le bleu.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La chaîne des balançoires se tait, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15715,7 +16715,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Lina montre vert. Maman a vu les balançoires. Et la dînette. On rit un peu. Lina essuie ses mains. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>Sarah a choisi vert. Elle a encore la dînette. On est près de les balançoires. La cuillère verte est tiède. Sarah demande. Papa dit oui. Elle pose la cuillère verte, tout doux. Raphaël a encore de l'énergie. On attend, un peu ? D'accord. Cette énergie n'est pas une faute. On peut jouer ou attendre. On peut demander à un adulte. Merci, maman. Bravo, Sarah. Tu as su attendre. C'est du bon travail. Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15855,7 +16855,24 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Lina montre vert. Maman a vu les balançoires. Et la dînette. On rit un peu. Lina essuie ses mains. Cette énergie n'est pas une faute. On peut jouer ou attendre. On joue, ou on attend. On peut demander à un adulte. Lina dit merci à maman.</t>
+          <t>narrateur|Sarah a choisi vert.
+narrateur|Elle a encore la dînette.
+narrateur|On est près de les balançoires.
+narrateur|La cuillère verte est tiède.
+narrateur|Sarah demande.
+narrateur|Papa dit oui.
+narrateur|Elle pose la cuillère verte, tout doux.
+narrateur|Raphaël a encore de l'énergie.
+enfant-f|On attend, un peu ?
+copain|D'accord.
+maman|Cette énergie n'est pas une faute.
+papa|On peut jouer ou attendre.
+papa|On peut demander à un adulte.
+enfant-f|Merci, maman.
+maman|Bravo, Sarah.
+maman|Tu as su attendre.
+papa|C'est du bon travail.
+narrateur|Ils jouent encore, un tout petit peu.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15883,7 +16900,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué. On a attendu. Bravo, Sarah. Tu as fait du bon travail. Sarah a vécu les balançoires, avec la dînette. Elle a choisi le vert. Raphaël a eu de l'énergie. Ce n'était pas une faute. La chaîne des balançoires se tait, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16023,7 +17040,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué.
+enfant-f|On a attendu.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vécu les balançoires, avec la dînette.
+narrateur|Elle a choisi le vert.
+narrateur|Raphaël a eu de l'énergie.
+narrateur|Ce n'était pas une faute.
+narrateur|La chaîne des balançoires se tait, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16045,7 +17071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16139,6 +17165,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-010.xlsx
+++ b/stories/arbres/TREE-DIF-010.xlsx
@@ -1385,12 +1385,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Trois couleurs attendent le saut. Le chapeau jaune, le ruban rouge, ou la dune verte. Lequel colore ton saut, Raphaël ?</t>
+          <t>Trois couleurs attendent le saut. Le jaune du chapeau, le rouge du ruban, le vert de la dune. Lequel colore ton saut, Raphaël ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Trois couleurs attendent le saut. Le chapeau jaune, le ruban rouge, ou la dune verte. Lequel colore ton saut, Raphaël ?</t>
+          <t>Trois couleurs attendent le saut. Le jaune du chapeau, le rouge du ruban, le vert de la dune. Lequel colore ton saut, Raphaël ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Trois couleurs attendent le saut.
-narrateur|Le chapeau jaune, le ruban rouge, ou la dune verte.
+narrateur|Le jaune du chapeau, le rouge du ruban, le vert de la dune.
 papa|Lequel colore ton saut, Raphaël ?</t>
         </is>
       </c>
@@ -2128,12 +2128,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Le chapeau jaune est sur sa tête, encore. Le chemin, le bac, ou la rampe. Où tu sautes, Raphaël ?</t>
+          <t>Le chapeau jaune est sur sa tête, encore. Le chemin de sable, le bac chaud, ou la rampe. Où tu sautes, Raphaël ?</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Le chapeau jaune est sur sa tête, encore. Le chemin, le bac, ou la rampe. Où tu sautes, Raphaël ?</t>
+          <t>Le chapeau jaune est sur sa tête, encore. Le chemin de sable, le bac chaud, ou la rampe. Où tu sautes, Raphaël ?</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       <c r="AW7" t="inlineStr">
         <is>
           <t>narrateur|Le chapeau jaune est sur sa tête, encore.
-narrateur|Le chemin, le bac, ou la rampe.
+narrateur|Le chemin de sable, le bac chaud, ou la rampe.
 papa|Où tu sautes, Raphaël ?</t>
         </is>
       </c>
@@ -3744,12 +3744,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Raphaël arrive au bac, le chapeau trop grand. Le sable du bac est chaud, un peu rêche. Je saute dedans ! Il saute, et l'aile jaune se remplit de grains. On dirait un seau, ton chapeau. Il est lourd, maintenant. Vide-le tout doux, pas en courant. Il penche l'aile, et l'or retombe. Un grain reste coincé dans la paille. Encore un saut ? Le bac t'attend, le chapeau aussi. Le jaune brille au fond du bac, tout petit.</t>
+          <t>Raphaël arrive au bac, le chapeau trop grand. Le sable du bac est chaud, un peu rêche. Je saute dedans ! Il saute, et l'aile jaune se remplit de grains. On dirait un seau, ton chapeau. Il est lourd, maintenant. Vide-le tout doux, en marchant. Il penche l'aile, et l'or retombe. Un grain reste coincé dans la paille. Encore un saut ? Le bac t'attend, le chapeau aussi. Le jaune brille au fond du bac, tout petit.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Raphaël arrive au bac, le chapeau trop grand. Le sable du bac est chaud, un peu rêche. Je saute dedans ! Il saute, et l'aile jaune se remplit de grains. On dirait un seau, ton chapeau. Il est lourd, maintenant. Vide-le tout doux, pas en courant. Il penche l'aile, et l'or retombe. Un grain reste coincé dans la paille. Encore un saut ? Le bac t'attend, le chapeau aussi. Le jaune brille au fond du bac, tout petit.</t>
+          <t>Raphaël arrive au bac, le chapeau trop grand. Le sable du bac est chaud, un peu rêche. Je saute dedans ! Il saute, et l'aile jaune se remplit de grains. On dirait un seau, ton chapeau. Il est lourd, maintenant. Vide-le tout doux, en marchant. Il penche l'aile, et l'or retombe. Un grain reste coincé dans la paille. Encore un saut ? Le bac t'attend, le chapeau aussi. Le jaune brille au fond du bac, tout petit.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
 narrateur|Il saute, et l'aile jaune se remplit de grains.
 maman|On dirait un seau, ton chapeau.
 enfant-m|Il est lourd, maintenant.
-papa|Vide-le tout doux, pas en courant.
+papa|Vide-le tout doux, en marchant.
 narrateur|Il penche l'aile, et l'or retombe.
 narrateur|Un grain reste coincé dans la paille.
 enfant-m|Encore un saut ?
@@ -4472,12 +4472,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>J'attends. Raphaël s'arrête dans le bac, le souffle encore haut. Il s'assoit au bord du bac, l'aile à plat. Un grain roule, puis plus rien. Le bac s'est tu. Tu peux sauter, tout petit. Il saute, et le chapeau reste sur les genoux d'abord.</t>
+          <t>J'attends. Raphaël s'arrête dans le bac, le souffle encore haut. Il s'assoit au bord du bac, l'aile à plat. Un grain roule, puis plus rien. Le bac s'est tu. Tu peux sauter, tout petit. Il remet l'aile, puis saute un tout petit saut.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>J'attends. Raphaël s'arrête dans le bac, le souffle encore haut. Il s'assoit au bord du bac, l'aile à plat. Un grain roule, puis plus rien. Le bac s'est tu. Tu peux sauter, tout petit. Il saute, et le chapeau reste sur les genoux d'abord.</t>
+          <t>J'attends. Raphaël s'arrête dans le bac, le souffle encore haut. Il s'assoit au bord du bac, l'aile à plat. Un grain roule, puis plus rien. Le bac s'est tu. Tu peux sauter, tout petit. Il remet l'aile, puis saute un tout petit saut.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
 narrateur|Un grain roule, puis plus rien.
 enfant-m|Le bac s'est tu.
 maman|Tu peux sauter, tout petit.
-narrateur|Il saute, et le chapeau reste sur les genoux d'abord.</t>
+narrateur|Il remet l'aile, puis saute un tout petit saut.</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>tissu</t>
+          <t>vent</t>
         </is>
       </c>
     </row>
@@ -7136,12 +7136,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Le ruban rouge est sur sa tête, encore. Le chemin, le bac, ou la rampe. Où tu sautes, Raphaël ?</t>
+          <t>Le ruban rouge est sur sa tête, encore. Le chemin de sable, le bac chaud, ou la rampe. Où tu sautes, Raphaël ?</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Le ruban rouge est sur sa tête, encore. Le chemin, le bac, ou la rampe. Où tu sautes, Raphaël ?</t>
+          <t>Le ruban rouge est sur sa tête, encore. Le chemin de sable, le bac chaud, ou la rampe. Où tu sautes, Raphaël ?</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       <c r="AW35" t="inlineStr">
         <is>
           <t>narrateur|Le ruban rouge est sur sa tête, encore.
-narrateur|Le chemin, le bac, ou la rampe.
+narrateur|Le chemin de sable, le bac chaud, ou la rampe.
 papa|Où tu sautes, Raphaël ?</t>
         </is>
       </c>
@@ -8752,12 +8752,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Raphaël penche le ruban au-dessus du bac. Le sable rose de l'ombre colle déjà. Il ne faut pas qu'il mange le sable. Alors on saute sans le laisser tomber. Il saute au bord, et le ruban plonge. Une virgule rouge dans le bac. Je le sors ! Il tire, trop fort, et le chapeau penche. Du sable tombe de l'aile, tout fin. Tout doux, le fil est mince. Je recommence le saut. Le ruban garde un grain, tout rouge de poussière.</t>
+          <t>Raphaël penche le ruban au-dessus du bac. Le sable rose de l'ombre colle déjà. Je le garde hors du sable. On saute, le ruban en l'air. Il saute au bord, et le ruban plonge. Une virgule rouge dans le bac. Je le sors ! Il tire, trop fort, et le chapeau penche. Du sable tombe de l'aile, tout fin. Tout doux, le fil est mince. Je recommence le saut. Le ruban garde un grain, tout rouge de poussière.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Raphaël penche le ruban au-dessus du bac. Le sable rose de l'ombre colle déjà. Il ne faut pas qu'il mange le sable. Alors on saute sans le laisser tomber. Il saute au bord, et le ruban plonge. Une virgule rouge dans le bac. Je le sors ! Il tire, trop fort, et le chapeau penche. Du sable tombe de l'aile, tout fin. Tout doux, le fil est mince. Je recommence le saut. Le ruban garde un grain, tout rouge de poussière.</t>
+          <t>Raphaël penche le ruban au-dessus du bac. Le sable rose de l'ombre colle déjà. Je le garde hors du sable. On saute, le ruban en l'air. Il saute au bord, et le ruban plonge. Une virgule rouge dans le bac. Je le sors ! Il tire, trop fort, et le chapeau penche. Du sable tombe de l'aile, tout fin. Tout doux, le fil est mince. Je recommence le saut. Le ruban garde un grain, tout rouge de poussière.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -8894,8 +8894,8 @@
         <is>
           <t>narrateur|Raphaël penche le ruban au-dessus du bac.
 narrateur|Le sable rose de l'ombre colle déjà.
-enfant-m|Il ne faut pas qu'il mange le sable.
-papa|Alors on saute sans le laisser tomber.
+enfant-m|Je le garde hors du sable.
+papa|On saute, le ruban en l'air.
 narrateur|Il saute au bord, et le ruban plonge.
 maman|Une virgule rouge dans le bac.
 enfant-m|Je le sors !
@@ -9480,12 +9480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>J'attends. Raphaël s'arrête dans le bac, le souffle encore haut. Il s'assoit au bord du bac, l'aile à plat. Un grain roule, puis plus rien. Le bac s'est tu. Tu peux sauter, tout petit. Il saute, et le chapeau reste sur les genoux d'abord.</t>
+          <t>J'attends. Raphaël s'arrête dans le bac, le souffle encore haut. Il s'assoit au bord du bac, l'aile à plat. Un grain roule, puis plus rien. Le bac s'est tu. Tu peux sauter, tout petit. Il remet l'aile, puis saute un tout petit saut.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>J'attends. Raphaël s'arrête dans le bac, le souffle encore haut. Il s'assoit au bord du bac, l'aile à plat. Un grain roule, puis plus rien. Le bac s'est tu. Tu peux sauter, tout petit. Il saute, et le chapeau reste sur les genoux d'abord.</t>
+          <t>J'attends. Raphaël s'arrête dans le bac, le souffle encore haut. Il s'assoit au bord du bac, l'aile à plat. Un grain roule, puis plus rien. Le bac s'est tu. Tu peux sauter, tout petit. Il remet l'aile, puis saute un tout petit saut.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -9626,7 +9626,7 @@
 narrateur|Un grain roule, puis plus rien.
 enfant-m|Le bac s'est tu.
 maman|Tu peux sauter, tout petit.
-narrateur|Il saute, et le chapeau reste sur les genoux d'abord.</t>
+narrateur|Il remet l'aile, puis saute un tout petit saut.</t>
         </is>
       </c>
     </row>
@@ -12144,12 +12144,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>La dune verte est sur sa tête, encore. Le chemin, le bac, ou la rampe. Où tu sautes, Raphaël ?</t>
+          <t>La dune verte est sur sa tête, encore. Le chemin de sable, le bac chaud, ou la rampe. Où tu sautes, Raphaël ?</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>La dune verte est sur sa tête, encore. Le chemin, le bac, ou la rampe. Où tu sautes, Raphaël ?</t>
+          <t>La dune verte est sur sa tête, encore. Le chemin de sable, le bac chaud, ou la rampe. Où tu sautes, Raphaël ?</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -12309,7 +12309,7 @@
       <c r="AW63" t="inlineStr">
         <is>
           <t>narrateur|La dune verte est sur sa tête, encore.
-narrateur|Le chemin, le bac, ou la rampe.
+narrateur|Le chemin de sable, le bac chaud, ou la rampe.
 papa|Où tu sautes, Raphaël ?</t>
         </is>
       </c>
@@ -14488,12 +14488,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>J'attends. Raphaël s'arrête dans le bac, le souffle encore haut. Il s'assoit au bord du bac, l'aile à plat. Un grain roule, puis plus rien. Le bac s'est tu. Tu peux sauter, tout petit. Il saute, et le chapeau reste sur les genoux d'abord.</t>
+          <t>J'attends. Raphaël s'arrête dans le bac, le souffle encore haut. Il s'assoit au bord du bac, l'aile à plat. Un grain roule, puis plus rien. Le bac s'est tu. Tu peux sauter, tout petit. Il remet l'aile, puis saute un tout petit saut.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>J'attends. Raphaël s'arrête dans le bac, le souffle encore haut. Il s'assoit au bord du bac, l'aile à plat. Un grain roule, puis plus rien. Le bac s'est tu. Tu peux sauter, tout petit. Il saute, et le chapeau reste sur les genoux d'abord.</t>
+          <t>J'attends. Raphaël s'arrête dans le bac, le souffle encore haut. Il s'assoit au bord du bac, l'aile à plat. Un grain roule, puis plus rien. Le bac s'est tu. Tu peux sauter, tout petit. Il remet l'aile, puis saute un tout petit saut.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -14634,7 +14634,7 @@
 narrateur|Un grain roule, puis plus rien.
 enfant-m|Le bac s'est tu.
 maman|Tu peux sauter, tout petit.
-narrateur|Il saute, et le chapeau reste sur les genoux d'abord.</t>
+narrateur|Il remet l'aile, puis saute un tout petit saut.</t>
         </is>
       </c>
     </row>
@@ -16600,7 +16600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16706,6 +16706,13 @@
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
